--- a/insurance_data/4_life/golf_leisure/extracted_data.xlsx
+++ b/insurance_data/4_life/golf_leisure/extracted_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT60"/>
+  <dimension ref="A1:AT82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9243,43 +9243,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DB손보</t>
+          <t>하나생명</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>(무)Top3 시그니처안심보험</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>골프중카트사고부상(1~10급)치료비</t>
+          <t>상과염수술급여금</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중에 국내 소재의 골프시설에서 골프 카트를 운전하던 중 또는 탑승중, 골프카트에 탑승하지 않고 운행중인 골프카트와의 충돌, 접촉 등 으로 발생한 우연한 사고로 인한 상해의 직접적인 결과로써 자동차손해배상보장법시행령에서 정한 자동차사고 부상등급표의 부상등급을 받은 경우 보험가입금액 한도로 부상등급에 따라 차등 지급.</t>
+          <t>피보험자가 보험기간 중 ‘상과염(테니스엘보, 골프엘보)’으 로 진단이 확정되고, 그 치료를 직접적인 목적으로 수술을 받았을 때</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>500만원</t>
+          <t>수술 1회당 60만원</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>500만원</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5,520 원</t>
+          <t>190,700 원</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>5,520 원</t>
+          <t>86,125 원</t>
         </is>
       </c>
       <c r="J51" t="inlineStr"/>
@@ -9294,71 +9298,139 @@
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (7).xls</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162045373.xls</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>하나생명</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>DB손보</t>
+          <t>(무)Top3 시그니처안심보험</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>골프중카트사고부상(1~10급)치료비</t>
+          <t>상과염수술급여금</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중에 국내 소재의 골프시설에서 골프 카트를 운전하던 중 또는 탑승중, 골프카트에 탑승하지 않고 운행중인 골프카트와의 충돌, 접촉 등 으로 발생한 우연한 사고로 인한 상해의 직접적인 결과로써 자동차손해배상보장법시행령에서 정한 자동차사고 부상등급표의 부상등급을 받은 경우 보험가입금액 한도로 부상등급에 따라 차등 지급.</t>
+          <t>피보험자가 보험기간 중 ‘상과염(테니스엘보, 골프엘보)’으 로 진단이 확정되고, 그 치료를 직접적인 목적으로 수술을 받았을 때</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>500만원</t>
+          <t>수술 1회당 60만원</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>5,520</t>
+          <t>3천만원</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>5,520</t>
+          <t>2288400  원</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>1,033,500  원</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>98.9</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr"/>
-      <c r="AB51" t="inlineStr"/>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
+          <t>3.25 %</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>101.2 %</t>
+        </is>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>100.0 %</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL51" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN51" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>1. 가입연령 : 20세 ~ 최대 75세 2. 보험기간 : 100세/110세 만기 3. 납입주기 : 연납/월납 4. 납입기간 : 3/4/5/7/10/15/20년납 5. 상품유형 : 표준형 6. 보험료 예시기준 : 40세, 100세 만기, 20년납, 월납, 가입금액 3,000만원 7. 보험가격지수 예시기준 : 40세, 100세만기, 20년납, 월납, 가입금액 3,000만원 8. 적용이율에 관한 사항 : 적용이율은 보험기간 5년 이내 연복리 3.25%, 5년 초과 10년 이내 연복리 2.75%, 10년 초과 연복리 1.75%</t>
+        </is>
+      </c>
+      <c r="AP51" t="inlineStr">
+        <is>
+          <t>1577-1112</t>
+        </is>
+      </c>
       <c r="AQ51" t="inlineStr"/>
       <c r="AR51" t="inlineStr"/>
       <c r="AS51" t="inlineStr"/>
@@ -9367,37 +9439,49 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DB손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>골프활동중 상해사망(보통약관)</t>
+          <t>특정 팔근육염증 및 내·외측상과염 진단자금</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간중 골프활동중 상해사고로 사망한 경우 가입금액 지급</t>
+          <t>피보험자가 보험기간 중 ‘특정 팔근육염증 및 내·외측상과염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>10000만원</t>
+          <t>5만원</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>10000만원</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>7,666 원</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>4,699 원</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
@@ -9410,47 +9494,139 @@
       <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (7).xls</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>골프활동중 상해사망(보통약관)</t>
+          <t>특정 팔근육염증 및 내·외측상과염 진단자금</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간중 골프활동중 상해사고로 사망한 경우 가입금액 지급</t>
+          <t>피보험자가 보험기간 중 ‘특정 팔근육염증 및 내·외측상과염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>10000만원</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="inlineStr"/>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr"/>
-      <c r="AA52" t="inlineStr"/>
-      <c r="AB52" t="inlineStr"/>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="inlineStr"/>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>7666  원</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>4,699  원</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>137.4 %</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>117.2 %</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ52" t="inlineStr"/>
       <c r="AR52" t="inlineStr"/>
       <c r="AS52" t="inlineStr"/>
@@ -9459,37 +9635,49 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DB손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>골프활동중배상책임(실손)</t>
+          <t>특정 다리근육염증 및 족저근막염 진단자금</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>보험기간중 피보험자가 골프시설구내에서 골프의 연습,경기 또는 지도중에 타인의 신체 및 재물에 대한 법률상 배상책임을 부담함으로써 입은 손해를 가입금액한도로 보상(본인부담금 2만원)</t>
+          <t>피보험자가 보험기간 중 ‘특정 다리근육염증 및 족저근막염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2000만원</t>
+          <t>5만원</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2000만원</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7,666 원</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>4,699 원</t>
+        </is>
+      </c>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
@@ -9502,47 +9690,139 @@
       <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (7).xls</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>골프활동중배상책임(실손)</t>
+          <t>특정 다리근육염증 및 족저근막염 진단자금</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>보험기간중 피보험자가 골프시설구내에서 골프의 연습,경기 또는 지도중에 타인의 신체 및 재물에 대한 법률상 배상책임을 부담함으로써 입은 손해를 가입금액한도로 보상(본인부담금 2만원)</t>
+          <t>피보험자가 보험기간 중 ‘특정 다리근육염증 및 족저근막염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>2000만원</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="inlineStr"/>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr"/>
-      <c r="AA53" t="inlineStr"/>
-      <c r="AB53" t="inlineStr"/>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>7666  원</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>4,699  원</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>137.4 %</t>
+        </is>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>117.2 %</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL53" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN53" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ53" t="inlineStr"/>
       <c r="AR53" t="inlineStr"/>
       <c r="AS53" t="inlineStr"/>
@@ -9551,37 +9831,49 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DB손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>알바트로스비용(깔때기홀제외)(정규홀,실손)</t>
+          <t>재해 특정 무릎인대파열 및 연골찢김 수술자금</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 알바트로스을 행한 경우 1회에 한하여 알바트로스를 행한 날로부터 1개월(단, 축하라운드의 경우 3개월) 이내 소요된 금액(약관에서 정한 항목 내)을 보험 가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘특정 무릎인대파열 및 연골찢김’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>100만원</t>
+          <t>50만원</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>100만원</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>7,666 원</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>4,699 원</t>
+        </is>
+      </c>
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
@@ -9594,47 +9886,139 @@
       <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (7).xls</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>알바트로스비용(깔때기홀제외)(정규홀,실손)</t>
+          <t>재해 특정 무릎인대파열 및 연골찢김 수술자금</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 알바트로스을 행한 경우 1회에 한하여 알바트로스를 행한 날로부터 1개월(단, 축하라운드의 경우 3개월) 이내 소요된 금액(약관에서 정한 항목 내)을 보험 가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘특정 무릎인대파열 및 연골찢김’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>100만원</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr"/>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>7666  원</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>4,699  원</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>137.4 %</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>117.2 %</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL54" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN54" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ54" t="inlineStr"/>
       <c r="AR54" t="inlineStr"/>
       <c r="AS54" t="inlineStr"/>
@@ -9643,29 +10027,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DB손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>홀인원비용(깔때기홀제외)(정규홀,실손)(연간1회한)</t>
+          <t>재해 아킬레스힘줄손상 수술자금</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 홀인원을 행한 경우 연간 1회에 한하여 홀인원을 행한 날부터 1개월(단, 축하라운드의 경우 3개월) 이내에 소요된 금액(약관에서 정한 항목 내)을 보험가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘아킬레스힘줄손상’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>25만원</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7,666 원</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4,699 원</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
@@ -9678,43 +10082,139 @@
       <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (7).xls</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>홀인원비용(깔때기홀제외)(정규홀,실손)(연간1회한)</t>
+          <t>재해 아킬레스힘줄손상 수술자금</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 홀인원을 행한 경우 연간 1회에 한하여 홀인원을 행한 날부터 1개월(단, 축하라운드의 경우 3개월) 이내에 소요된 금액(약관에서 정한 항목 내)을 보험가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="inlineStr"/>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr"/>
-      <c r="AA55" t="inlineStr"/>
-      <c r="AB55" t="inlineStr"/>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘아킬레스힘줄손상’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>25만원</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>7666  원</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>4,699  원</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>137.4 %</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>117.2 %</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ55" t="inlineStr"/>
       <c r="AR55" t="inlineStr"/>
       <c r="AS55" t="inlineStr"/>
@@ -9723,43 +10223,47 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>한화손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한화 다이렉트 홀인원보험 (무)2601</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>골프존스크린골프장홀인원비용(실손)</t>
+          <t>재해 탈구, 염좌 및 과긴장 수술자금</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>약관에서 정한 스크린골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한함) 보상 (연간1회에 한하고, 깔때기홀, 가상골프장 및 멀리건 플레이시 행한 홀인원 제외)</t>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘탈구, 염좌 및 과긴장’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(1회당)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상</t>
+          <t>5만원</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상</t>
+          <t>50만원  원</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6,011 원</t>
+          <t>7,666 원</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6,011 원</t>
+          <t>4,699 원</t>
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
@@ -9774,71 +10278,139 @@
       <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (9).xls</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>한화손보</t>
+          <t>한화생명 간편가입 포켓레저보험 무배당</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>한화 다이렉트 홀인원보험 (무)2601</t>
+          <t>주계약</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>골프존스크린골프장홀인원비용(실손)</t>
+          <t>재해 탈구, 염좌 및 과긴장 수술자금</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>약관에서 정한 스크린골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한함) 보상 (연간1회에 한하고, 깔때기홀, 가상골프장 및 멀리건 플레이시 행한 홀인원 제외)</t>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘탈구, 염좌 및 과긴장’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(1회당)</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상</t>
+          <t>5만원</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>6,011</t>
+          <t>50만원  원</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>6,011</t>
+          <t>7666  원</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>4,699  원</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>137.4 %</t>
+        </is>
+      </c>
+      <c r="AD56" t="inlineStr">
+        <is>
+          <t>117.2 %</t>
+        </is>
+      </c>
+      <c r="AE56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN56" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ56" t="inlineStr"/>
       <c r="AR56" t="inlineStr"/>
       <c r="AS56" t="inlineStr"/>
@@ -9847,37 +10419,49 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>한화손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>한화 다이렉트 홀인원보험 (무)2601</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>골프활동중배상책임(2만원공제)</t>
+          <t>특정 팔근육염증 및 내·외측상과염 진단자금</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>피보험자가 골프시설 구내(골프의 연습 또는 경기를 행하는 시설을 말하며, 골프연습장, 탈의실 등 그 외 부속시설 포함)에서 골프의 연습. 경기 또는 지도(이에 따른 탈의, 휴식 포함) 중에 생긴 우연한 사고로 피보험자가 타인의 신체 또는 재물에 대한 법률상의 배상책임 부담함으로써 입은 손해</t>
+          <t>피보험자가 보험기간 중 ‘특정 팔근육염증 및 내·외측상과염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상(자기부담금 : 2만원)</t>
+          <t>5만원</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상(자기부담금 : 2만원)</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>4,376 원</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2,906 원</t>
+        </is>
+      </c>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
@@ -9890,47 +10474,139 @@
       <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (9).xls</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr"/>
-      <c r="R57" t="inlineStr"/>
-      <c r="S57" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>골프활동중배상책임(2만원공제)</t>
+          <t>특정 팔근육염증 및 내·외측상과염 진단자금</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>피보험자가 골프시설 구내(골프의 연습 또는 경기를 행하는 시설을 말하며, 골프연습장, 탈의실 등 그 외 부속시설 포함)에서 골프의 연습. 경기 또는 지도(이에 따른 탈의, 휴식 포함) 중에 생긴 우연한 사고로 피보험자가 타인의 신체 또는 재물에 대한 법률상의 배상책임 부담함으로써 입은 손해</t>
+          <t>피보험자가 보험기간 중 ‘특정 팔근육염증 및 내·외측상과염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상(자기부담금 : 2만원)</t>
-        </is>
-      </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="inlineStr"/>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr"/>
-      <c r="AA57" t="inlineStr"/>
-      <c r="AB57" t="inlineStr"/>
-      <c r="AC57" t="inlineStr"/>
-      <c r="AD57" t="inlineStr"/>
-      <c r="AE57" t="inlineStr"/>
-      <c r="AF57" t="inlineStr"/>
-      <c r="AG57" t="inlineStr"/>
-      <c r="AH57" t="inlineStr"/>
-      <c r="AI57" t="inlineStr"/>
-      <c r="AJ57" t="inlineStr"/>
-      <c r="AK57" t="inlineStr"/>
-      <c r="AL57" t="inlineStr"/>
-      <c r="AM57" t="inlineStr"/>
-      <c r="AN57" t="inlineStr"/>
-      <c r="AO57" t="inlineStr"/>
-      <c r="AP57" t="inlineStr"/>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>4376  원</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2,906  원</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>78.4 %</t>
+        </is>
+      </c>
+      <c r="AD57" t="inlineStr">
+        <is>
+          <t>72.5 %</t>
+        </is>
+      </c>
+      <c r="AE57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN57" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ57" t="inlineStr"/>
       <c r="AR57" t="inlineStr"/>
       <c r="AS57" t="inlineStr"/>
@@ -9939,37 +10615,49 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>한화손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한화 다이렉트 홀인원보험 (무)2601</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>두번째홀인원비용(실손,1회한)</t>
+          <t>특정 다리근육염증 및 족저근막염 진단자금</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>약관에서 정한 골프장에서 골프경기 중 두 번째 홀인원을 행한 후 두 번째 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액)보상</t>
+          <t>피보험자가 보험기간 중 ‘특정 다리근육염증 및 족저근막염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상 (최초1회에 한하며, 깔때기홀은 제외)</t>
+          <t>5만원</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상 (최초1회에 한하며, 깔때기홀은 제외)</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>4,376 원</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2,906 원</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr">
         <is>
@@ -9982,47 +10670,139 @@
       <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (9).xls</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr"/>
-      <c r="R58" t="inlineStr"/>
-      <c r="S58" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>두번째홀인원비용(실손,1회한)</t>
+          <t>특정 다리근육염증 및 족저근막염 진단자금</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>약관에서 정한 골프장에서 골프경기 중 두 번째 홀인원을 행한 후 두 번째 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액)보상</t>
+          <t>피보험자가 보험기간 중 ‘특정 다리근육염증 및 족저근막염’으로 진단이 확정되었을 경우(최초 1회한)</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
         <is>
-          <t>보험가입금액 한도 실손보상 (최초1회에 한하며, 깔때기홀은 제외)</t>
-        </is>
-      </c>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="inlineStr"/>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr"/>
-      <c r="AA58" t="inlineStr"/>
-      <c r="AB58" t="inlineStr"/>
-      <c r="AC58" t="inlineStr"/>
-      <c r="AD58" t="inlineStr"/>
-      <c r="AE58" t="inlineStr"/>
-      <c r="AF58" t="inlineStr"/>
-      <c r="AG58" t="inlineStr"/>
-      <c r="AH58" t="inlineStr"/>
-      <c r="AI58" t="inlineStr"/>
-      <c r="AJ58" t="inlineStr"/>
-      <c r="AK58" t="inlineStr"/>
-      <c r="AL58" t="inlineStr"/>
-      <c r="AM58" t="inlineStr"/>
-      <c r="AN58" t="inlineStr"/>
-      <c r="AO58" t="inlineStr"/>
-      <c r="AP58" t="inlineStr"/>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>4376  원</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2,906  원</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>78.4 %</t>
+        </is>
+      </c>
+      <c r="AD58" t="inlineStr">
+        <is>
+          <t>72.5 %</t>
+        </is>
+      </c>
+      <c r="AE58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN58" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ58" t="inlineStr"/>
       <c r="AR58" t="inlineStr"/>
       <c r="AS58" t="inlineStr"/>
@@ -10031,29 +10811,49 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>한화손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>한화 다이렉트 홀인원보험 (무)2601</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>알바트로스비용(실손,1회한)</t>
+          <t>재해 특정 무릎인대파열 및 연골찢김 수술자금</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>약관에서 정한 골프장에서 골프경기 중 알바트로스를 행한 경우 알바트로스를 행한 날부터 1개월 이내에 소요된 비용 (약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘특정 무릎인대파열 및 연골찢김’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>4,376 원</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>2,906 원</t>
+        </is>
+      </c>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
@@ -10066,43 +10866,139 @@
       <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (9).xls</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr"/>
-      <c r="R59" t="inlineStr"/>
-      <c r="S59" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>알바트로스비용(실손,1회한)</t>
+          <t>재해 특정 무릎인대파열 및 연골찢김 수술자금</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>약관에서 정한 골프장에서 골프경기 중 알바트로스를 행한 경우 알바트로스를 행한 날부터 1개월 이내에 소요된 비용 (약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
-        </is>
-      </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="inlineStr"/>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr"/>
-      <c r="AA59" t="inlineStr"/>
-      <c r="AB59" t="inlineStr"/>
-      <c r="AC59" t="inlineStr"/>
-      <c r="AD59" t="inlineStr"/>
-      <c r="AE59" t="inlineStr"/>
-      <c r="AF59" t="inlineStr"/>
-      <c r="AG59" t="inlineStr"/>
-      <c r="AH59" t="inlineStr"/>
-      <c r="AI59" t="inlineStr"/>
-      <c r="AJ59" t="inlineStr"/>
-      <c r="AK59" t="inlineStr"/>
-      <c r="AL59" t="inlineStr"/>
-      <c r="AM59" t="inlineStr"/>
-      <c r="AN59" t="inlineStr"/>
-      <c r="AO59" t="inlineStr"/>
-      <c r="AP59" t="inlineStr"/>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘특정 무릎인대파열 및 연골찢김’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>4376  원</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2,906  원</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>78.4 %</t>
+        </is>
+      </c>
+      <c r="AD59" t="inlineStr">
+        <is>
+          <t>72.5 %</t>
+        </is>
+      </c>
+      <c r="AE59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN59" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ59" t="inlineStr"/>
       <c r="AR59" t="inlineStr"/>
       <c r="AS59" t="inlineStr"/>
@@ -10111,29 +11007,49 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>한화손보</t>
+          <t>한화생명</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>한화 다이렉트 홀인원보험 (무)2601</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>홀인원비용(실손,1회한)</t>
+          <t>재해 아킬레스힘줄손상 수술자금</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>약관에서 정한 골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘아킬레스힘줄손상’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>25만원</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>4,376 원</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2,906 원</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
@@ -10146,48 +11062,3444 @@
       <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>장기보장성 비교 공시 (9).xls</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr"/>
-      <c r="R60" t="inlineStr"/>
-      <c r="S60" t="inlineStr"/>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>홀인원비용(실손,1회한)</t>
+          <t>재해 아킬레스힘줄손상 수술자금</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
         <is>
-          <t>약관에서 정한 골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="inlineStr"/>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr"/>
-      <c r="AA60" t="inlineStr"/>
-      <c r="AB60" t="inlineStr"/>
-      <c r="AC60" t="inlineStr"/>
-      <c r="AD60" t="inlineStr"/>
-      <c r="AE60" t="inlineStr"/>
-      <c r="AF60" t="inlineStr"/>
-      <c r="AG60" t="inlineStr"/>
-      <c r="AH60" t="inlineStr"/>
-      <c r="AI60" t="inlineStr"/>
-      <c r="AJ60" t="inlineStr"/>
-      <c r="AK60" t="inlineStr"/>
-      <c r="AL60" t="inlineStr"/>
-      <c r="AM60" t="inlineStr"/>
-      <c r="AN60" t="inlineStr"/>
-      <c r="AO60" t="inlineStr"/>
-      <c r="AP60" t="inlineStr"/>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘아킬레스힘줄손상’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(최초 1회한)</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>25만원</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>4376  원</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2,906  원</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>78.4 %</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>72.5 %</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
       <c r="AQ60" t="inlineStr"/>
       <c r="AR60" t="inlineStr"/>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr"/>
     </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>재해 탈구, 염좌 및 과긴장 수술자금</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘탈구, 염좌 및 과긴장’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(1회당)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>4,376 원</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>2,906 원</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>한화생명</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>한화생명 포켓레저보험 무배당</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>재해 탈구, 염좌 및 과긴장 수술자금</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 발생한 재해를 직접적인 원인으로 ‘탈구, 염좌 및 과긴장’으로 진단이 확정되고, 보험기간 중 그 치료를 직접적인 목적으로 수술을 받았을 경우(1회당)</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>5만원</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>50만원  원</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>4376  원</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2,906  원</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>2.50 %</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>78.4 %</t>
+        </is>
+      </c>
+      <c r="AD61" t="inlineStr">
+        <is>
+          <t>72.5 %</t>
+        </is>
+      </c>
+      <c r="AE61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>무해지/저해지환급</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="AN61" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 만 19세 ~ 65세 2. 납입주기 : 일시납 3. 가입한도 : 보험가입금액 50만원 4. 보험기간 : 1년만기 5. 보험가격지수 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 6. 보험료 기준 : 40세, 1년만기, 일시납, 주계약가입금액 50만원 7. 확정이율 : 2.50% * 특약 : 부가가능 특약 無</t>
+        </is>
+      </c>
+      <c r="AP61" t="inlineStr">
+        <is>
+          <t>1588-6363</t>
+        </is>
+      </c>
+      <c r="AQ61" t="inlineStr"/>
+      <c r="AR61" t="inlineStr"/>
+      <c r="AS61" t="inlineStr"/>
+      <c r="AT61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>뺑소니,무보험차 교통재해 장해급여금</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 제3조(“뺑소니,무보험차 교통재해”의 정의)에서 정한 뺑소니 ？ 무보험차에 의한 교통재해로 인하여 장해분류표에서 정한 장해지급률에 해당하는 장해상태가 되었을 때</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>남자 1,000만원 × 해당 장해지급률 / 여자 2,000만원 × 해당 장해지급률</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>뺑소니,무보험차 교통재해 장해급여금</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 제3조(“뺑소니,무보험차 교통재해”의 정의)에서 정한 뺑소니 ？ 무보험차에 의한 교통재해로 인하여 장해분류표에서 정한 장해지급률에 해당하는 장해상태가 되었을 때</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>남자 1,000만원 × 해당 장해지급률 / 여자 2,000만원 × 해당 장해지급률</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>3000  원</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>3,000  원</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>2.75 %</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>121.0 %</t>
+        </is>
+      </c>
+      <c r="AD62" t="inlineStr">
+        <is>
+          <t>70.4 %</t>
+        </is>
+      </c>
+      <c r="AE62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>대면채널</t>
+        </is>
+      </c>
+      <c r="AN62" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 자녀형(0세~20세), 레저형 및 성인형(만15세~65세) 2. 보험기간 : 1년 3. 보험료 예시기준 : 1형(자녀형), 가입금액 1구좌(10만원), 1년만기, 일시납, 5세</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>1588-2288</t>
+        </is>
+      </c>
+      <c r="AQ62" t="inlineStr"/>
+      <c r="AR62" t="inlineStr"/>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>일반재해 장해급여금</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 발생한 뺑소니,무보험차에 의한 교통재해 이외의 재해로 인하여 장해분류표에서 정한 장해지급률에 해당하는 장해상태가 되었을 때</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>남자 300만원 × 해당 장해지급률 / 여자 600만원 × 해당 장해지급률</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>일반재해 장해급여금</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 발생한 뺑소니,무보험차에 의한 교통재해 이외의 재해로 인하여 장해분류표에서 정한 장해지급률에 해당하는 장해상태가 되었을 때</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>남자 300만원 × 해당 장해지급률 / 여자 600만원 × 해당 장해지급률</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>3000  원</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>3,000  원</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>2.75 %</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>121.0 %</t>
+        </is>
+      </c>
+      <c r="AD63" t="inlineStr">
+        <is>
+          <t>70.4 %</t>
+        </is>
+      </c>
+      <c r="AE63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>대면채널</t>
+        </is>
+      </c>
+      <c r="AN63" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 자녀형(0세~20세), 레저형 및 성인형(만15세~65세) 2. 보험기간 : 1년 3. 보험료 예시기준 : 1형(자녀형), 가입금액 1구좌(10만원), 1년만기, 일시납, 5세</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>1588-2288</t>
+        </is>
+      </c>
+      <c r="AQ63" t="inlineStr"/>
+      <c r="AR63" t="inlineStr"/>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>재해골절 (치아파절 제외) 수술비</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 재해로 인하여 제4조(“재해골절(치아파절 제외)”의 정의 및 진단확정)에서 정한 골절상태가 되어 그 치료를 직접적인 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>남자 10만원 / 여자 20만원</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>재해골절 (치아파절 제외) 수술비</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 재해로 인하여 제4조(“재해골절(치아파절 제외)”의 정의 및 진단확정)에서 정한 골절상태가 되어 그 치료를 직접적인 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>남자 10만원 / 여자 20만원</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>3000  원</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>3,000  원</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>2.75 %</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>121.0 %</t>
+        </is>
+      </c>
+      <c r="AD64" t="inlineStr">
+        <is>
+          <t>70.4 %</t>
+        </is>
+      </c>
+      <c r="AE64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>대면채널</t>
+        </is>
+      </c>
+      <c r="AN64" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 자녀형(0세~20세), 레저형 및 성인형(만15세~65세) 2. 보험기간 : 1년 3. 보험료 예시기준 : 1형(자녀형), 가입금액 1구좌(10만원), 1년만기, 일시납, 5세</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>1588-2288</t>
+        </is>
+      </c>
+      <c r="AQ64" t="inlineStr"/>
+      <c r="AR64" t="inlineStr"/>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>화상 및 부식 입원비</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 재해를 직접적인 원인으로 화상 및 부식 이 진단확정되고 그 화상 및 부식치료를 직접목적으로 하여 11일이상 계속입원 하였을 때(110일 한도, 10일초과 1일당)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>남자 5만원 / 여자 10만원</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3,000 원</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>흥국생명</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>(무)처음만난흥국생명상해보험</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>화상 및 부식 입원비</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중 보장개시일 이후에 재해를 직접적인 원인으로 화상 및 부식 이 진단확정되고 그 화상 및 부식치료를 직접목적으로 하여 11일이상 계속입원 하였을 때(110일 한도, 10일초과 1일당)</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>남자 5만원 / 여자 10만원</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>3000  원</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>3,000  원</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>2.75 %</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>121.0 %</t>
+        </is>
+      </c>
+      <c r="AD65" t="inlineStr">
+        <is>
+          <t>70.4 %</t>
+        </is>
+      </c>
+      <c r="AE65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>보험기간(1년 이하)</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>대면채널</t>
+        </is>
+      </c>
+      <c r="AN65" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>1. 가입나이 : 자녀형(0세~20세), 레저형 및 성인형(만15세~65세) 2. 보험기간 : 1년 3. 보험료 예시기준 : 1형(자녀형), 가입금액 1구좌(10만원), 1년만기, 일시납, 5세</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>1588-2288</t>
+        </is>
+      </c>
+      <c r="AQ65" t="inlineStr"/>
+      <c r="AR65" t="inlineStr"/>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>교통재해사망보험금</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 “교통재해”로 인하여 사망하였을 때</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>10,000만원</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>10,100 원</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>7,000 원</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>교통재해사망보험금</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 “교통재해”로 인하여 사망하였을 때</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>10,000만원</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>10100  원</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>7,000  원</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>3.00 %</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>157.4 %</t>
+        </is>
+      </c>
+      <c r="AD66" t="inlineStr">
+        <is>
+          <t>229.8 %</t>
+        </is>
+      </c>
+      <c r="AE66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI66" t="inlineStr">
+        <is>
+          <t>보험기간(1년 초과)</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL66" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>대면채널  방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN66" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>1. 상품형태: 3종(레저보장형) 2. 보험기간: 10년만기 3. 납입주기: 월납 4. 가입연령: 15세 ~ 최고 75세 5. 보험가격지수 예시기준: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 6. 보험료 예시기준 - 주계약: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 ※기타 자세한 사항은 상품요약서 참조</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>1588-3131</t>
+        </is>
+      </c>
+      <c r="AQ66" t="inlineStr"/>
+      <c r="AR66" t="inlineStr"/>
+      <c r="AS66" t="inlineStr"/>
+      <c r="AT66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>교통재해장해보험금</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 동일한 교통재해를 직접적인 원인으로 장해분류표에서 정한 장해지급률 중 3%이상 100%이하에 해당하는 장해상태가 되었을 때</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>1,000만원 × 해당장해지급율</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>10,100 원</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>7,000 원</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>교통재해장해보험금</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 동일한 교통재해를 직접적인 원인으로 장해분류표에서 정한 장해지급률 중 3%이상 100%이하에 해당하는 장해상태가 되었을 때</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>1,000만원 × 해당장해지급율</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>10100  원</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>7,000  원</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>3.00 %</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>157.4 %</t>
+        </is>
+      </c>
+      <c r="AD67" t="inlineStr">
+        <is>
+          <t>229.8 %</t>
+        </is>
+      </c>
+      <c r="AE67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>보험기간(1년 초과)</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL67" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>대면채널  방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN67" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>1. 상품형태: 3종(레저보장형) 2. 보험기간: 10년만기 3. 납입주기: 월납 4. 가입연령: 15세 ~ 최고 75세 5. 보험가격지수 예시기준: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 6. 보험료 예시기준 - 주계약: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 ※기타 자세한 사항은 상품요약서 참조</t>
+        </is>
+      </c>
+      <c r="AP67" t="inlineStr">
+        <is>
+          <t>1588-3131</t>
+        </is>
+      </c>
+      <c r="AQ67" t="inlineStr"/>
+      <c r="AR67" t="inlineStr"/>
+      <c r="AS67" t="inlineStr"/>
+      <c r="AT67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>재해수술급여금</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해의 치료를 직접적인 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>10,100 원</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>7,000 원</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>재해수술급여금</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해의 치료를 직접적인 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>10100  원</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>7,000  원</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>3.00 %</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>157.4 %</t>
+        </is>
+      </c>
+      <c r="AD68" t="inlineStr">
+        <is>
+          <t>229.8 %</t>
+        </is>
+      </c>
+      <c r="AE68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>보험기간(1년 초과)</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL68" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>대면채널  방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN68" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>1. 상품형태: 3종(레저보장형) 2. 보험기간: 10년만기 3. 납입주기: 월납 4. 가입연령: 15세 ~ 최고 75세 5. 보험가격지수 예시기준: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 6. 보험료 예시기준 - 주계약: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 ※기타 자세한 사항은 상품요약서 참조</t>
+        </is>
+      </c>
+      <c r="AP68" t="inlineStr">
+        <is>
+          <t>1588-3131</t>
+        </is>
+      </c>
+      <c r="AQ68" t="inlineStr"/>
+      <c r="AR68" t="inlineStr"/>
+      <c r="AS68" t="inlineStr"/>
+      <c r="AT68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>재해골절치료비</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해를 원인으로 재해골절(치아파절 제외) 상태가 되었을 때(발생 1회당)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>10,100 원</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>7,000 원</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>재해골절치료비</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해를 원인으로 재해골절(치아파절 제외) 상태가 되었을 때(발생 1회당)</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>10100  원</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>7,000  원</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>3.00 %</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>157.4 %</t>
+        </is>
+      </c>
+      <c r="AD69" t="inlineStr">
+        <is>
+          <t>229.8 %</t>
+        </is>
+      </c>
+      <c r="AE69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>보험기간(1년 초과)</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL69" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>대면채널  방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN69" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>1. 상품형태: 3종(레저보장형) 2. 보험기간: 10년만기 3. 납입주기: 월납 4. 가입연령: 15세 ~ 최고 75세 5. 보험가격지수 예시기준: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 6. 보험료 예시기준 - 주계약: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 ※기타 자세한 사항은 상품요약서 참조</t>
+        </is>
+      </c>
+      <c r="AP69" t="inlineStr">
+        <is>
+          <t>1588-3131</t>
+        </is>
+      </c>
+      <c r="AQ69" t="inlineStr"/>
+      <c r="AR69" t="inlineStr"/>
+      <c r="AS69" t="inlineStr"/>
+      <c r="AT69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>아킬레스힘줄손상 수술급여금</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해를 직접적인 원인으로 아킬레스힘줄손상으로 진단확정되고, 그 직접적인 치료를 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>10,100 원</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>7,000 원</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>아킬레스힘줄손상 수술급여금</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해를 직접적인 원인으로 아킬레스힘줄손상으로 진단확정되고, 그 직접적인 치료를 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>50만원</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>10100  원</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>7,000  원</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>3.00 %</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>157.4 %</t>
+        </is>
+      </c>
+      <c r="AD70" t="inlineStr">
+        <is>
+          <t>229.8 %</t>
+        </is>
+      </c>
+      <c r="AE70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>보험기간(1년 초과)</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL70" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>대면채널  방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN70" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>1. 상품형태: 3종(레저보장형) 2. 보험기간: 10년만기 3. 납입주기: 월납 4. 가입연령: 15세 ~ 최고 75세 5. 보험가격지수 예시기준: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 6. 보험료 예시기준 - 주계약: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 ※기타 자세한 사항은 상품요약서 참조</t>
+        </is>
+      </c>
+      <c r="AP70" t="inlineStr">
+        <is>
+          <t>1588-3131</t>
+        </is>
+      </c>
+      <c r="AQ70" t="inlineStr"/>
+      <c r="AR70" t="inlineStr"/>
+      <c r="AS70" t="inlineStr"/>
+      <c r="AT70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>무릎인대파열·연골손상 수술급여금</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해를 직접적인 원인으로 무릎인대파열·연골손상으로 진단확정되고, 그 직접적인 치료를 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>20만원</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>10,100 원</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>7,000 원</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>무릎인대파열·연골손상 수술급여금</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 재해를 직접적인 원인으로 무릎인대파열·연골손상으로 진단확정되고, 그 직접적인 치료를 목적으로 수술을 받았을 때(수술 1회당)</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>20만원</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>10100  원</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>7,000  원</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>3.00 %</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>157.4 %</t>
+        </is>
+      </c>
+      <c r="AD71" t="inlineStr">
+        <is>
+          <t>229.8 %</t>
+        </is>
+      </c>
+      <c r="AE71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>보험기간(1년 초과)</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL71" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>대면채널  방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN71" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>1. 상품형태: 3종(레저보장형) 2. 보험기간: 10년만기 3. 납입주기: 월납 4. 가입연령: 15세 ~ 최고 75세 5. 보험가격지수 예시기준: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 6. 보험료 예시기준 - 주계약: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 ※기타 자세한 사항은 상품요약서 참조</t>
+        </is>
+      </c>
+      <c r="AP71" t="inlineStr">
+        <is>
+          <t>1588-3131</t>
+        </is>
+      </c>
+      <c r="AQ71" t="inlineStr"/>
+      <c r="AR71" t="inlineStr"/>
+      <c r="AS71" t="inlineStr"/>
+      <c r="AT71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>내측상과염(골프엘보우) 진단자금</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 내측상과염으로 진단확정 되었을 때(최초 1회에 한함)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>10,100 원</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>7,000 원</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>보장성_상품비교_20260608162059302.xls</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>DB생명</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>(무)백년친구 생활보험(2602)(3종:레저보장형)</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>주계약</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>내측상과염(골프엘보우) 진단자금</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>보험기간 중 피보험자가 내측상과염으로 진단확정 되었을 때(최초 1회에 한함)</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>10만원</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>1,000만원  원</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>10100  원</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>7,000  원</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>3.00 %</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>157.4 %</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>229.8 %</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>보험기간(1년 초과)</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>순수보장</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>비유니버셜</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>대면채널  방카슈랑스</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>1. 상품형태: 3종(레저보장형) 2. 보험기간: 10년만기 3. 납입주기: 월납 4. 가입연령: 15세 ~ 최고 75세 5. 보험가격지수 예시기준: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 6. 보험료 예시기준 - 주계약: 3종(레저보장형), 가입금액형, 가입나이 40세, 보험기간 10년, 2년납, 월납 ※기타 자세한 사항은 상품요약서 참조</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>1588-3131</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr"/>
+      <c r="AR72" t="inlineStr"/>
+      <c r="AS72" t="inlineStr"/>
+      <c r="AT72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>골프중카트사고부상(1~10급)치료비</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중에 국내 소재의 골프시설에서 골프 카트를 운전하던 중 또는 탑승중, 골프카트에 탑승하지 않고 운행중인 골프카트와의 충돌, 접촉 등 으로 발생한 우연한 사고로 인한 상해의 직접적인 결과로써 자동차손해배상보장법시행령에서 정한 자동차사고 부상등급표의 부상등급을 받은 경우 보험가입금액 한도로 부상등급에 따라 차등 지급.</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>5,520 원</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>5,520 원</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (7).xls</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr"/>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>골프중카트사고부상(1~10급)치료비</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중에 국내 소재의 골프시설에서 골프 카트를 운전하던 중 또는 탑승중, 골프카트에 탑승하지 않고 운행중인 골프카트와의 충돌, 접촉 등 으로 발생한 우연한 사고로 인한 상해의 직접적인 결과로써 자동차손해배상보장법시행령에서 정한 자동차사고 부상등급표의 부상등급을 받은 경우 보험가입금액 한도로 부상등급에 따라 차등 지급.</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>500만원</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>5,520</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>5,520</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>98.9</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr"/>
+      <c r="AB73" t="inlineStr"/>
+      <c r="AC73" t="inlineStr"/>
+      <c r="AD73" t="inlineStr"/>
+      <c r="AE73" t="inlineStr"/>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="inlineStr"/>
+      <c r="AH73" t="inlineStr"/>
+      <c r="AI73" t="inlineStr"/>
+      <c r="AJ73" t="inlineStr"/>
+      <c r="AK73" t="inlineStr"/>
+      <c r="AL73" t="inlineStr"/>
+      <c r="AM73" t="inlineStr"/>
+      <c r="AN73" t="inlineStr"/>
+      <c r="AO73" t="inlineStr"/>
+      <c r="AP73" t="inlineStr"/>
+      <c r="AQ73" t="inlineStr"/>
+      <c r="AR73" t="inlineStr"/>
+      <c r="AS73" t="inlineStr"/>
+      <c r="AT73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>골프활동중 상해사망(보통약관)</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간중 골프활동중 상해사고로 사망한 경우 가입금액 지급</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>10000만원</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>10000만원</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (7).xls</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr"/>
+      <c r="R74" t="inlineStr"/>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>골프활동중 상해사망(보통약관)</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간중 골프활동중 상해사고로 사망한 경우 가입금액 지급</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>10000만원</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
+      <c r="AA74" t="inlineStr"/>
+      <c r="AB74" t="inlineStr"/>
+      <c r="AC74" t="inlineStr"/>
+      <c r="AD74" t="inlineStr"/>
+      <c r="AE74" t="inlineStr"/>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="inlineStr"/>
+      <c r="AH74" t="inlineStr"/>
+      <c r="AI74" t="inlineStr"/>
+      <c r="AJ74" t="inlineStr"/>
+      <c r="AK74" t="inlineStr"/>
+      <c r="AL74" t="inlineStr"/>
+      <c r="AM74" t="inlineStr"/>
+      <c r="AN74" t="inlineStr"/>
+      <c r="AO74" t="inlineStr"/>
+      <c r="AP74" t="inlineStr"/>
+      <c r="AQ74" t="inlineStr"/>
+      <c r="AR74" t="inlineStr"/>
+      <c r="AS74" t="inlineStr"/>
+      <c r="AT74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>골프활동중배상책임(실손)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>보험기간중 피보험자가 골프시설구내에서 골프의 연습,경기 또는 지도중에 타인의 신체 및 재물에 대한 법률상 배상책임을 부담함으로써 입은 손해를 가입금액한도로 보상(본인부담금 2만원)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (7).xls</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr"/>
+      <c r="R75" t="inlineStr"/>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>골프활동중배상책임(실손)</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>보험기간중 피보험자가 골프시설구내에서 골프의 연습,경기 또는 지도중에 타인의 신체 및 재물에 대한 법률상 배상책임을 부담함으로써 입은 손해를 가입금액한도로 보상(본인부담금 2만원)</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>2000만원</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
+      <c r="AA75" t="inlineStr"/>
+      <c r="AB75" t="inlineStr"/>
+      <c r="AC75" t="inlineStr"/>
+      <c r="AD75" t="inlineStr"/>
+      <c r="AE75" t="inlineStr"/>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="inlineStr"/>
+      <c r="AH75" t="inlineStr"/>
+      <c r="AI75" t="inlineStr"/>
+      <c r="AJ75" t="inlineStr"/>
+      <c r="AK75" t="inlineStr"/>
+      <c r="AL75" t="inlineStr"/>
+      <c r="AM75" t="inlineStr"/>
+      <c r="AN75" t="inlineStr"/>
+      <c r="AO75" t="inlineStr"/>
+      <c r="AP75" t="inlineStr"/>
+      <c r="AQ75" t="inlineStr"/>
+      <c r="AR75" t="inlineStr"/>
+      <c r="AS75" t="inlineStr"/>
+      <c r="AT75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>알바트로스비용(깔때기홀제외)(정규홀,실손)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 알바트로스을 행한 경우 1회에 한하여 알바트로스를 행한 날로부터 1개월(단, 축하라운드의 경우 3개월) 이내 소요된 금액(약관에서 정한 항목 내)을 보험 가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (7).xls</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr"/>
+      <c r="R76" t="inlineStr"/>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>알바트로스비용(깔때기홀제외)(정규홀,실손)</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 알바트로스을 행한 경우 1회에 한하여 알바트로스를 행한 날로부터 1개월(단, 축하라운드의 경우 3개월) 이내 소요된 금액(약관에서 정한 항목 내)을 보험 가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>100만원</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
+      <c r="AA76" t="inlineStr"/>
+      <c r="AB76" t="inlineStr"/>
+      <c r="AC76" t="inlineStr"/>
+      <c r="AD76" t="inlineStr"/>
+      <c r="AE76" t="inlineStr"/>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="inlineStr"/>
+      <c r="AH76" t="inlineStr"/>
+      <c r="AI76" t="inlineStr"/>
+      <c r="AJ76" t="inlineStr"/>
+      <c r="AK76" t="inlineStr"/>
+      <c r="AL76" t="inlineStr"/>
+      <c r="AM76" t="inlineStr"/>
+      <c r="AN76" t="inlineStr"/>
+      <c r="AO76" t="inlineStr"/>
+      <c r="AP76" t="inlineStr"/>
+      <c r="AQ76" t="inlineStr"/>
+      <c r="AR76" t="inlineStr"/>
+      <c r="AS76" t="inlineStr"/>
+      <c r="AT76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>DB손보</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>(무)다이렉트 오잘공 골프보험2601(CM)</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>홀인원비용(깔때기홀제외)(정규홀,실손)(연간1회한)</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 홀인원을 행한 경우 연간 1회에 한하여 홀인원을 행한 날부터 1개월(단, 축하라운드의 경우 3개월) 이내에 소요된 금액(약관에서 정한 항목 내)을 보험가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (7).xls</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr"/>
+      <c r="R77" t="inlineStr"/>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>홀인원비용(깔때기홀제외)(정규홀,실손)(연간1회한)</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>피보험자가 보험기간 중에 골프장에서 골프경기 중 홀인원을 행한 경우 연간 1회에 한하여 홀인원을 행한 날부터 1개월(단, 축하라운드의 경우 3개월) 이내에 소요된 금액(약관에서 정한 항목 내)을 보험가입금액을 한도로 지급(18홀 이상을 보유한 국내 소재의 회원제골프장 및 정규대중골프장에 한함)</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
+      <c r="AA77" t="inlineStr"/>
+      <c r="AB77" t="inlineStr"/>
+      <c r="AC77" t="inlineStr"/>
+      <c r="AD77" t="inlineStr"/>
+      <c r="AE77" t="inlineStr"/>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="inlineStr"/>
+      <c r="AH77" t="inlineStr"/>
+      <c r="AI77" t="inlineStr"/>
+      <c r="AJ77" t="inlineStr"/>
+      <c r="AK77" t="inlineStr"/>
+      <c r="AL77" t="inlineStr"/>
+      <c r="AM77" t="inlineStr"/>
+      <c r="AN77" t="inlineStr"/>
+      <c r="AO77" t="inlineStr"/>
+      <c r="AP77" t="inlineStr"/>
+      <c r="AQ77" t="inlineStr"/>
+      <c r="AR77" t="inlineStr"/>
+      <c r="AS77" t="inlineStr"/>
+      <c r="AT77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>한화손보</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>한화 다이렉트 홀인원보험 (무)2604</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>골프존스크린골프장홀인원비용(실손)</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>약관에서 정한 스크린골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한함) 보상 (연간1회에 한하고, 깔때기홀, 가상골프장 및 멀리건 플레이시 행한 홀인원 제외)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>6,006 원</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>6,006 원</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (9).xls</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr"/>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>한화손보</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>한화 다이렉트 홀인원보험 (무)2604</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>골프존스크린골프장홀인원비용(실손)</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>약관에서 정한 스크린골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한함) 보상 (연간1회에 한하고, 깔때기홀, 가상골프장 및 멀리건 플레이시 행한 홀인원 제외)</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>6,006</t>
+        </is>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>6,006</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr"/>
+      <c r="AB78" t="inlineStr"/>
+      <c r="AC78" t="inlineStr"/>
+      <c r="AD78" t="inlineStr"/>
+      <c r="AE78" t="inlineStr"/>
+      <c r="AF78" t="inlineStr"/>
+      <c r="AG78" t="inlineStr"/>
+      <c r="AH78" t="inlineStr"/>
+      <c r="AI78" t="inlineStr"/>
+      <c r="AJ78" t="inlineStr"/>
+      <c r="AK78" t="inlineStr"/>
+      <c r="AL78" t="inlineStr"/>
+      <c r="AM78" t="inlineStr"/>
+      <c r="AN78" t="inlineStr"/>
+      <c r="AO78" t="inlineStr"/>
+      <c r="AP78" t="inlineStr"/>
+      <c r="AQ78" t="inlineStr"/>
+      <c r="AR78" t="inlineStr"/>
+      <c r="AS78" t="inlineStr"/>
+      <c r="AT78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>한화손보</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>한화 다이렉트 홀인원보험 (무)2604</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>골프활동중배상책임(2만원공제)</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>피보험자가 골프시설 구내(골프의 연습 또는 경기를 행하는 시설을 말하며, 골프연습장, 탈의실 등 그 외 부속시설 포함)에서 골프의 연습. 경기 또는 지도(이에 따른 탈의, 휴식 포함) 중에 생긴 우연한 사고로 피보험자가 타인의 신체 또는 재물에 대한 법률상의 배상책임 부담함으로써 입은 손해</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상(자기부담금 : 2만원)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상(자기부담금 : 2만원)</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (9).xls</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>골프활동중배상책임(2만원공제)</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>피보험자가 골프시설 구내(골프의 연습 또는 경기를 행하는 시설을 말하며, 골프연습장, 탈의실 등 그 외 부속시설 포함)에서 골프의 연습. 경기 또는 지도(이에 따른 탈의, 휴식 포함) 중에 생긴 우연한 사고로 피보험자가 타인의 신체 또는 재물에 대한 법률상의 배상책임 부담함으로써 입은 손해</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상(자기부담금 : 2만원)</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
+      <c r="AA79" t="inlineStr"/>
+      <c r="AB79" t="inlineStr"/>
+      <c r="AC79" t="inlineStr"/>
+      <c r="AD79" t="inlineStr"/>
+      <c r="AE79" t="inlineStr"/>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="inlineStr"/>
+      <c r="AH79" t="inlineStr"/>
+      <c r="AI79" t="inlineStr"/>
+      <c r="AJ79" t="inlineStr"/>
+      <c r="AK79" t="inlineStr"/>
+      <c r="AL79" t="inlineStr"/>
+      <c r="AM79" t="inlineStr"/>
+      <c r="AN79" t="inlineStr"/>
+      <c r="AO79" t="inlineStr"/>
+      <c r="AP79" t="inlineStr"/>
+      <c r="AQ79" t="inlineStr"/>
+      <c r="AR79" t="inlineStr"/>
+      <c r="AS79" t="inlineStr"/>
+      <c r="AT79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>한화손보</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>한화 다이렉트 홀인원보험 (무)2604</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>두번째홀인원비용(실손,1회한)</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>약관에서 정한 골프장에서 골프경기 중 두 번째 홀인원을 행한 후 두 번째 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액)보상</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상 (최초1회에 한하며, 깔때기홀은 제외)</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상 (최초1회에 한하며, 깔때기홀은 제외)</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (9).xls</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr"/>
+      <c r="R80" t="inlineStr"/>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>두번째홀인원비용(실손,1회한)</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>약관에서 정한 골프장에서 골프경기 중 두 번째 홀인원을 행한 후 두 번째 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액)보상</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>보험가입금액 한도 실손보상 (최초1회에 한하며, 깔때기홀은 제외)</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
+      <c r="AA80" t="inlineStr"/>
+      <c r="AB80" t="inlineStr"/>
+      <c r="AC80" t="inlineStr"/>
+      <c r="AD80" t="inlineStr"/>
+      <c r="AE80" t="inlineStr"/>
+      <c r="AF80" t="inlineStr"/>
+      <c r="AG80" t="inlineStr"/>
+      <c r="AH80" t="inlineStr"/>
+      <c r="AI80" t="inlineStr"/>
+      <c r="AJ80" t="inlineStr"/>
+      <c r="AK80" t="inlineStr"/>
+      <c r="AL80" t="inlineStr"/>
+      <c r="AM80" t="inlineStr"/>
+      <c r="AN80" t="inlineStr"/>
+      <c r="AO80" t="inlineStr"/>
+      <c r="AP80" t="inlineStr"/>
+      <c r="AQ80" t="inlineStr"/>
+      <c r="AR80" t="inlineStr"/>
+      <c r="AS80" t="inlineStr"/>
+      <c r="AT80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>한화손보</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>한화 다이렉트 홀인원보험 (무)2604</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>알바트로스비용(실손,1회한)</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>약관에서 정한 골프장에서 골프경기 중 알바트로스를 행한 경우 알바트로스를 행한 날부터 1개월 이내에 소요된 비용 (약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (9).xls</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr"/>
+      <c r="R81" t="inlineStr"/>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>알바트로스비용(실손,1회한)</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>약관에서 정한 골프장에서 골프경기 중 알바트로스를 행한 경우 알바트로스를 행한 날부터 1개월 이내에 소요된 비용 (약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr"/>
+      <c r="AB81" t="inlineStr"/>
+      <c r="AC81" t="inlineStr"/>
+      <c r="AD81" t="inlineStr"/>
+      <c r="AE81" t="inlineStr"/>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="inlineStr"/>
+      <c r="AH81" t="inlineStr"/>
+      <c r="AI81" t="inlineStr"/>
+      <c r="AJ81" t="inlineStr"/>
+      <c r="AK81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr"/>
+      <c r="AM81" t="inlineStr"/>
+      <c r="AN81" t="inlineStr"/>
+      <c r="AO81" t="inlineStr"/>
+      <c r="AP81" t="inlineStr"/>
+      <c r="AQ81" t="inlineStr"/>
+      <c r="AR81" t="inlineStr"/>
+      <c r="AS81" t="inlineStr"/>
+      <c r="AT81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>한화손보</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>한화 다이렉트 홀인원보험 (무)2604</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>홀인원비용(실손,1회한)</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>약관에서 정한 골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>비갱신형</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>장기보장성 비교 공시 (9).xls</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>홀인원비용(실손,1회한)</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>약관에서 정한 골프장에서 골프경기 중 홀인원을 행한 후 홀인원을 행한 날부터 1개월 이내에 소요된 비용(약관에서 정한 비용에 한하며, 축하라운드 비용은 3개월 이내에 소요된 금액) 보상</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr"/>
+      <c r="AB82" t="inlineStr"/>
+      <c r="AC82" t="inlineStr"/>
+      <c r="AD82" t="inlineStr"/>
+      <c r="AE82" t="inlineStr"/>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="inlineStr"/>
+      <c r="AH82" t="inlineStr"/>
+      <c r="AI82" t="inlineStr"/>
+      <c r="AJ82" t="inlineStr"/>
+      <c r="AK82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr"/>
+      <c r="AM82" t="inlineStr"/>
+      <c r="AN82" t="inlineStr"/>
+      <c r="AO82" t="inlineStr"/>
+      <c r="AP82" t="inlineStr"/>
+      <c r="AQ82" t="inlineStr"/>
+      <c r="AR82" t="inlineStr"/>
+      <c r="AS82" t="inlineStr"/>
+      <c r="AT82" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
